--- a/data/trans_dic/P32C-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,45</t>
+          <t>1,29; 5,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,42</t>
+          <t>0,93; 4,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,69</t>
+          <t>0,38; 3,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 13,36</t>
+          <t>0,16; 12,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,1</t>
+          <t>1,22; 4,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,08</t>
+          <t>0,68; 3,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,23; 2,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,29</t>
+          <t>0,06; 5,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,88</t>
+          <t>0,94; 3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,56</t>
+          <t>0,78; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,85</t>
+          <t>0,84; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,13</t>
+          <t>0,47; 5,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,08</t>
+          <t>0,41; 4,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,35</t>
+          <t>1,08; 3,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,53</t>
+          <t>0,54; 2,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,12</t>
+          <t>0,87; 3,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,0</t>
+          <t>0,22; 2,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,32</t>
+          <t>1,34; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,57</t>
+          <t>0,24; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,21</t>
+          <t>0,36; 3,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,53</t>
+          <t>0,17; 1,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,74</t>
+          <t>0,82; 2,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,61</t>
+          <t>0,14; 1,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,38</t>
+          <t>0,37; 2,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,38</t>
+          <t>0,29; 3,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,98</t>
+          <t>1,12; 4,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,51</t>
+          <t>0,27; 2,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,52</t>
+          <t>0,25; 2,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,22</t>
+          <t>0,37; 3,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,95</t>
+          <t>0,38; 2,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,15</t>
+          <t>0,72; 3,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,29</t>
+          <t>0,49; 2,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,66</t>
+          <t>0,18; 1,58</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,78</t>
+          <t>1,54; 6,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,27</t>
+          <t>0,35; 3,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,35</t>
+          <t>1,21; 5,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,25</t>
+          <t>1,17; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,0</t>
+          <t>0,47; 4,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,98</t>
+          <t>1,04; 4,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,98</t>
+          <t>0,48; 3,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,9</t>
+          <t>0,83; 3,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,1</t>
+          <t>1,23; 3,95</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,39</t>
+          <t>0,64; 5,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,69</t>
+          <t>0,53; 4,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,64</t>
+          <t>0,62; 3,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,91</t>
+          <t>0,47; 3,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,34</t>
+          <t>0,38; 3,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,89</t>
+          <t>0,1; 2,01</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,37</t>
+          <t>1,08; 10,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,19</t>
+          <t>0,69; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,62</t>
+          <t>0,91; 8,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,02</t>
+          <t>0,86; 4,99</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,65</t>
+          <t>1,34; 2,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,8</t>
+          <t>1,43; 2,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,25</t>
+          <t>1,11; 2,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,74</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,83</t>
+          <t>0,39; 1,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,22</t>
+          <t>0,19; 1,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,83</t>
+          <t>0,33; 1,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,15</t>
+          <t>1,14; 2,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,94</t>
+          <t>1,02; 1,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,67</t>
+          <t>0,88; 1,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,55</t>
+          <t>0,71; 1,53</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3781; 15295</t>
+          <t>3619; 15173</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2553; 12302</t>
+          <t>2602; 12746</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>968; 9241</t>
+          <t>962; 9440</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4582</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7752</t>
+          <t>0; 8372</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>0; 5299</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1859</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169; 13473</t>
+          <t>163; 12804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5223; 19133</t>
+          <t>5712; 20092</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3350; 14157</t>
+          <t>3135; 14042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 9682</t>
+          <t>963; 8360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>180; 14319</t>
+          <t>165; 13946</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4923; 19430</t>
+          <t>4731; 18507</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3652; 16533</t>
+          <t>3637; 16217</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3016; 13999</t>
+          <t>3061; 14092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2830</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1022; 11197</t>
+          <t>1018; 11913</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>928; 9096</t>
+          <t>919; 9125</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 4519</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7861; 24086</t>
+          <t>7776; 25141</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3691; 17125</t>
+          <t>3660; 15648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4965; 18279</t>
+          <t>5125; 17984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4325</t>
+          <t>0; 5268</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>881; 8047</t>
+          <t>879; 8410</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5744; 18471</t>
+          <t>5728; 19356</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1018; 10992</t>
+          <t>1026; 11096</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1021; 9044</t>
+          <t>1029; 8860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6229</t>
+          <t>0; 4768</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2082</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4592</t>
+          <t>0; 4374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1013; 9567</t>
+          <t>1039; 8970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5969; 18324</t>
+          <t>5511; 18245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1022; 10836</t>
+          <t>931; 10615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1810; 10306</t>
+          <t>1619; 10859</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>909; 10593</t>
+          <t>916; 10911</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4257; 19628</t>
+          <t>4402; 18762</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1060; 9765</t>
+          <t>1063; 10873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886; 8685</t>
+          <t>847; 8399</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5089</t>
+          <t>0; 4498</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>983; 8463</t>
+          <t>985; 9120</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1137</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1752; 13512</t>
+          <t>1749; 12469</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4418; 19115</t>
+          <t>4386; 20673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3097; 14913</t>
+          <t>3180; 15633</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>884; 8891</t>
+          <t>986; 8482</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2645; 12213</t>
+          <t>2771; 12342</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>797; 7477</t>
+          <t>804; 7114</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2331; 15128</t>
+          <t>3420; 15968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3588; 13807</t>
+          <t>3085; 12414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 7293</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2185</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>578; 5392</t>
+          <t>638; 5389</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2677; 12736</t>
+          <t>2649; 12484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1633; 10157</t>
+          <t>1640; 10649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3447; 15964</t>
+          <t>3413; 15939</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5623; 16299</t>
+          <t>4909; 15721</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3900</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>991; 8268</t>
+          <t>982; 8499</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>915; 8183</t>
+          <t>919; 7972</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1186; 6922</t>
+          <t>1169; 6751</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1752</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2088</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3418</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4558</t>
+          <t>0; 3885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>727; 8185</t>
+          <t>985; 8238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>917; 8081</t>
+          <t>927; 8602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>329; 8882</t>
+          <t>462; 9419</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>808; 7584</t>
+          <t>787; 7642</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5418</t>
+          <t>0; 6370</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>572; 6196</t>
+          <t>694; 6317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2083</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2679</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2304</t>
+          <t>0; 2177</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>799; 7731</t>
+          <t>813; 8050</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2171</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 6207</t>
+          <t>0; 6379</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>974; 6363</t>
+          <t>1086; 6328</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24534; 49733</t>
+          <t>25161; 49639</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29656; 56954</t>
+          <t>29063; 54709</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22488; 44608</t>
+          <t>22072; 45121</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11182; 27422</t>
+          <t>12648; 27601</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3529; 16377</t>
+          <t>3470; 17009</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1001; 9173</t>
+          <t>997; 8400</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2921; 13756</t>
+          <t>2095; 12883</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3608; 18783</t>
+          <t>3393; 18061</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31280; 59731</t>
+          <t>31509; 57626</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31615; 59712</t>
+          <t>31268; 59237</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27679; 52044</t>
+          <t>27460; 51938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>19245; 40527</t>
+          <t>18427; 39892</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32C-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,41</t>
+          <t>1,33; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,58</t>
+          <t>1,06; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,77</t>
+          <t>0,38; 3,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 12,7</t>
+          <t>1,51; 14,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,3</t>
+          <t>1,1; 3,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,06</t>
+          <t>0,74; 2,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,0</t>
+          <t>0,23; 2,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,15</t>
+          <t>0,59; 5,71</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,69</t>
+          <t>1,1; 4,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,49</t>
+          <t>0,79; 3,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,88</t>
+          <t>0,83; 3,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,46</t>
+          <t>0,46; 4,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,09</t>
+          <t>0,41; 3,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,5</t>
+          <t>1,03; 3,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,31</t>
+          <t>0,55; 2,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,07</t>
+          <t>0,87; 3,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,09</t>
+          <t>0,22; 2,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,53</t>
+          <t>1,39; 4,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,6</t>
+          <t>0,24; 2,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,14</t>
+          <t>0,36; 3,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,16; 1,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,73</t>
+          <t>0,83; 2,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,57</t>
+          <t>0,15; 1,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,51</t>
+          <t>0,33; 2,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,48</t>
+          <t>0,29; 3,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,76</t>
+          <t>1,31; 5,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,79</t>
+          <t>0,27; 2,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,44</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,47</t>
+          <t>0,38; 3,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,72</t>
+          <t>0,25; 2,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,4</t>
+          <t>0,69; 3,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,4</t>
+          <t>0,49; 2,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,58</t>
+          <t>0,16; 1,6</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,85</t>
+          <t>1,51; 7,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,11</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,65</t>
+          <t>1,19; 5,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,72</t>
+          <t>1,16; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,0</t>
+          <t>0,43; 4,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,89</t>
+          <t>1,04; 4,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,13</t>
+          <t>0,52; 3,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,9</t>
+          <t>0,83; 4,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,95</t>
+          <t>1,13; 3,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,54</t>
+          <t>0,63; 5,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,57</t>
+          <t>0,52; 5,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,55</t>
+          <t>0,54; 3,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,94</t>
+          <t>0,47; 3,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,55</t>
+          <t>0,38; 3,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,01</t>
+          <t>0,46; 2,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,45</t>
+          <t>1,09; 10,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,32</t>
+          <t>0,52; 5,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,98</t>
+          <t>0,91; 8,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,99</t>
+          <t>0,66; 4,46</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,64</t>
+          <t>1,3; 2,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,69</t>
+          <t>1,5; 2,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,28</t>
+          <t>1,12; 2,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,78; 1,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,9</t>
+          <t>0,41; 1,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,81</t>
+          <t>0,1; 0,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,14</t>
+          <t>0,19; 1,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,76</t>
+          <t>0,56; 2,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,08</t>
+          <t>1,13; 2,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,93</t>
+          <t>1,04; 1,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,67</t>
+          <t>0,86; 1,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,53</t>
+          <t>0,85; 1,76</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3619; 15173</t>
+          <t>3732; 15330</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2602; 12746</t>
+          <t>2963; 13236</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>962; 9440</t>
+          <t>957; 9596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8372</t>
+          <t>0; 8164</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5299</t>
+          <t>0; 4742</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,27 +2103,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>163; 12804</t>
+          <t>1699; 16308</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5712; 20092</t>
+          <t>5118; 18431</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3135; 14042</t>
+          <t>3388; 13629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>963; 8360</t>
+          <t>969; 8470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>165; 13946</t>
+          <t>1659; 15943</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4731; 18507</t>
+          <t>5513; 20609</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3637; 16217</t>
+          <t>3665; 15644</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3061; 14092</t>
+          <t>3007; 13471</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1018; 11913</t>
+          <t>1012; 10380</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2306,32 +2306,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>919; 9125</t>
+          <t>917; 8039</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7776; 25141</t>
+          <t>7437; 23613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3660; 15648</t>
+          <t>3707; 17485</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5125; 17984</t>
+          <t>5084; 18136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5268</t>
+          <t>0; 5998</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4748</t>
         </is>
       </c>
     </row>
@@ -2484,27 +2484,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>879; 8410</t>
+          <t>865; 8375</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5728; 19356</t>
+          <t>5953; 19865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1026; 11096</t>
+          <t>1029; 10674</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1029; 8860</t>
+          <t>1127; 10026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4768</t>
+          <t>0; 5087</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2519,27 +2519,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4374</t>
+          <t>0; 4804</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1039; 8970</t>
+          <t>1020; 9897</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5511; 18245</t>
+          <t>5573; 19282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931; 10615</t>
+          <t>1026; 11184</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1619; 10859</t>
+          <t>1604; 10476</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>4035</t>
         </is>
       </c>
     </row>
@@ -2692,27 +2692,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>916; 10911</t>
+          <t>911; 11805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4402; 18762</t>
+          <t>5175; 19732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1063; 10873</t>
+          <t>1063; 9698</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>847; 8399</t>
+          <t>1129; 10003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4498</t>
+          <t>0; 4161</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>985; 9120</t>
+          <t>988; 8616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2732,22 +2732,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1749; 12469</t>
+          <t>1127; 12542</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4386; 20673</t>
+          <t>4205; 18354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3180; 15633</t>
+          <t>3215; 14997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>986; 8482</t>
+          <t>914; 9090</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9149</t>
         </is>
       </c>
     </row>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2771; 12342</t>
+          <t>2712; 12957</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>804; 7114</t>
+          <t>799; 7222</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3420; 15968</t>
+          <t>3376; 16024</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3085; 12414</t>
+          <t>3255; 13644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7293</t>
+          <t>0; 7129</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2935,27 +2935,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>638; 5389</t>
+          <t>636; 6081</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2649; 12484</t>
+          <t>2667; 12274</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1640; 10649</t>
+          <t>1768; 10297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3413; 15939</t>
+          <t>3402; 17008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4909; 15721</t>
+          <t>4849; 16465</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3652</t>
         </is>
       </c>
     </row>
@@ -3108,22 +3108,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>0; 3758</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>982; 8499</t>
+          <t>969; 8473</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>919; 7972</t>
+          <t>916; 8963</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1169; 6751</t>
+          <t>1123; 6778</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,27 +3143,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>0; 2739</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3885</t>
+          <t>0; 3864</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>985; 8238</t>
+          <t>979; 8084</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>927; 8602</t>
+          <t>910; 8073</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>462; 9419</t>
+          <t>1314; 7563</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2879</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>787; 7642</t>
+          <t>799; 7383</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6370</t>
+          <t>0; 6204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>694; 6317</t>
+          <t>568; 5850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2177</t>
+          <t>0; 2265</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>813; 8050</t>
+          <t>817; 7218</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 6379</t>
+          <t>0; 5622</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1086; 6328</t>
+          <t>924; 6274</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>31502</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25161; 49639</t>
+          <t>24416; 48743</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29063; 54709</t>
+          <t>30521; 56367</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22072; 45121</t>
+          <t>22204; 44470</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12648; 27601</t>
+          <t>13181; 29087</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3470; 17009</t>
+          <t>3702; 16168</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>997; 8400</t>
+          <t>992; 8150</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2095; 12883</t>
+          <t>2095; 12297</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3393; 18061</t>
+          <t>5046; 23533</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31509; 57626</t>
+          <t>31482; 57897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31268; 59237</t>
+          <t>31979; 58695</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27460; 51938</t>
+          <t>26676; 51967</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18427; 39892</t>
+          <t>21866; 45461</t>
         </is>
       </c>
     </row>
